--- a/Configs/GameConfig/Datas/dialogue.xlsx
+++ b/Configs/GameConfig/Datas/dialogue.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -75,15 +75,12 @@
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
+    <t>string</t>
   </si>
   <si>
     <t>DialogueType</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>(list#sep=@),DialogueChoice</t>
   </si>
   <si>
@@ -126,13 +123,76 @@
     <t>你好</t>
   </si>
   <si>
+    <t>10001_01</t>
+  </si>
+  <si>
     <t>张三</t>
   </si>
   <si>
     <t>你也好</t>
   </si>
   <si>
+    <t>10001_02</t>
+  </si>
+  <si>
     <t>End</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>你想吃什么</t>
+  </si>
+  <si>
+    <t>10002_01</t>
+  </si>
+  <si>
+    <t>都可以</t>
+  </si>
+  <si>
+    <t>10002_02</t>
+  </si>
+  <si>
+    <t>汉堡和麻辣烫选一个</t>
+  </si>
+  <si>
+    <t>10002_03</t>
+  </si>
+  <si>
+    <t>Choice</t>
+  </si>
+  <si>
+    <t>汉堡吧;10002_04_01@麻辣烫吧;10002_05_01</t>
+  </si>
+  <si>
+    <t>10002_04_01</t>
+  </si>
+  <si>
+    <t>汉堡太贵了</t>
+  </si>
+  <si>
+    <t>10002_04_02</t>
+  </si>
+  <si>
+    <t>那就麻辣烫呗</t>
+  </si>
+  <si>
+    <t>10002_04_03</t>
+  </si>
+  <si>
+    <t>GOGO</t>
+  </si>
+  <si>
+    <t>10002_04_04</t>
+  </si>
+  <si>
+    <t>10002_05_01</t>
+  </si>
+  <si>
+    <t>我也这么觉得，GOGO</t>
+  </si>
+  <si>
+    <t>10002_05_02</t>
   </si>
 </sst>
 </file>
@@ -1095,16 +1155,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="16.375" style="3" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="5" max="5" width="21.25" customWidth="1"/>
     <col min="6" max="6" width="20.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26.25" customWidth="1"/>
+    <col min="7" max="7" width="38.125" customWidth="1"/>
     <col min="8" max="8" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1187,19 +1247,19 @@
         <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
@@ -1219,7 +1279,7 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:23">
       <c r="A4" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1246,28 +1306,28 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:23">
       <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -1290,24 +1350,24 @@
         <v>10001</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3">
-        <v>1000101</v>
-      </c>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="3">
-        <v>1000101</v>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1315,18 +1375,173 @@
       <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="3">
-        <v>1000102</v>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="2:6">
-      <c r="B8" s="3">
-        <v>1000102</v>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" customFormat="1" spans="2:6">
+      <c r="B10" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="2:6">
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="2:6">
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="2:6">
+      <c r="B17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
